--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:09</t>
+    <t xml:space="preserve">2026-09-09 22:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:07</t>
+    <t xml:space="preserve">2026-09-17 13:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1243,18 +1243,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>463106.28</v>
+        <v>398297.44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>376921.69</v>
+        <v>463106.28</v>
       </c>
     </row>
     <row r="4">
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>398297.44</v>
+        <v>376921.69</v>
       </c>
     </row>
   </sheetData>
@@ -1327,101 +1327,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>312231.62</v>
+        <v>360401.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>379893.59</v>
+        <v>398297.44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>409024.62</v>
+        <v>408794.03</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>414068.28</v>
+        <v>312231.62</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>463106.28</v>
+        <v>379893.59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>473423.97</v>
+        <v>409024.62</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>340114.97</v>
+        <v>414068.28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>376921.69</v>
+        <v>463106.28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>385324.84</v>
+        <v>473423.97</v>
       </c>
     </row>
     <row r="11">
@@ -1558,35 +1558,35 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>360401.69</v>
+        <v>340114.97</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>398297.44</v>
+        <v>376921.69</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>408794.03</v>
+        <v>385324.84</v>
       </c>
     </row>
     <row r="26">

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:37</t>
+    <t xml:space="preserve">2026-09-25 21:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -608,7 +608,7 @@
         <v>204098.73</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>24314.46</v>
+        <v>24314.45</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>11.91</v>
@@ -654,7 +654,7 @@
         <v>287002.53</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>28255.35</v>
+        <v>28255.34</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>9.84</v>
@@ -677,7 +677,7 @@
         <v>241089.69</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>28297.37</v>
+        <v>28297.38</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>11.74</v>
@@ -700,7 +700,7 @@
         <v>416174.59</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>37085.85</v>
+        <v>37085.84</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>8.91</v>
@@ -746,7 +746,7 @@
         <v>252430.94</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>31281.18</v>
+        <v>31281.19</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>12.39</v>
@@ -815,7 +815,7 @@
         <v>311141.38</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>64467.96</v>
+        <v>64467.97</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>20.72</v>
@@ -884,7 +884,7 @@
         <v>254870.2</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>32052.99</v>
+        <v>32052.98</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>12.58</v>
@@ -953,7 +953,7 @@
         <v>276678.84</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>33896.35</v>
+        <v>33896.34</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>12.25</v>
@@ -1022,7 +1022,7 @@
         <v>241739.62</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>31991.6</v>
+        <v>31991.59</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>13.23</v>
@@ -1091,7 +1091,7 @@
         <v>263889.91</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>35316.65</v>
+        <v>35316.66</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>13.38</v>

--- a/output/laminas_provinciales/prov_i_ingr_mean_a_2023_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_ingr_mean_a_2023_valparaiso.xlsx
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:35</t>
+    <t xml:space="preserve">2026-10-05 07:04</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
